--- a/kriteria-2-knowledge-check-submissions.xlsx
+++ b/kriteria-2-knowledge-check-submissions.xlsx
@@ -414,12 +414,15 @@
     <t>Dalam penerapan algoritma Naive Bayes, Anda perlu menghitung nilai likelihood sebagai bagian dari algoritmanya. Bagaimana cara menghitung nilai likelihood dalam algoritma Naive Bayes jika data atau atribut yang digunakan bertipe kontinu?</t>
   </si>
   <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Dalam soal yang dikerjakan, Anda diminta melakukan perhitungan distribusi binomial menggunakan probability mass function (PMF). Mengapa pendekatan ini yang digunakan?</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
-    <t>Dalam soal yang dikerjakan, Anda diminta melakukan perhitungan distribusi binomial menggunakan probability mass function (PMF). Mengapa pendekatan ini yang digunakan?</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -538,9 +541,6 @@
       <t xml:space="preserve">Salah satu komponen dalam rumus tersebut adalah nilai p̂ (proporsi gabungan). Apa rumus yang digunakan untuk menghitung proporsi gabungan tersebut?
 </t>
     </r>
-  </si>
-  <si>
-    <t>D</t>
   </si>
   <si>
     <t>Berdasarkan hasil analisis, hipotesis nol ditolak pada tingkat signifikansi 0,05. Apa interpretasi yang paling tepat untuk menggambarkan kondisi ini?</t>
@@ -1194,7 +1194,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1236,7 +1236,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -1267,7 +1267,7 @@
         <v>1.0</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>24</v>
@@ -1278,10 +1278,10 @@
         <v>2.0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -1289,7 +1289,7 @@
         <v>3.0</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>24</v>
@@ -1300,7 +1300,7 @@
         <v>4.0</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>24</v>
@@ -1311,10 +1311,10 @@
         <v>5.0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1356,7 +1356,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -1387,7 +1387,7 @@
         <v>1.0</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>9</v>
@@ -1398,7 +1398,7 @@
         <v>2.0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>9</v>
@@ -1409,10 +1409,10 @@
         <v>3.0</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
